--- a/pacjenci/SYLWIA GMER.xlsx
+++ b/pacjenci/SYLWIA GMER.xlsx
@@ -413,235 +413,176 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>Nr badania</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>Data badania</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Nr badania</t>
-        </is>
-      </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Etap leczenia</t>
+          <t>Problem kliniczny</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Linia leczenia</t>
+          <t>Zakres badania</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Rozpoznanie</t>
+          <t>Opis badania</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Opis</t>
+          <t>Wnioski</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
           <t>SUVmax</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Ocena odpowiedzi</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Deauville</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Wnioski</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
         <is>
           <t>06.09.2022</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>1</v>
-      </c>
       <c r="C2" t="inlineStr">
         <is>
           <t>Chłoniak Hodgkina- rozpoznanie z ww chłonnych pod MOS po stronie lewej. Ocena stopnia zaawansowania przed leczeniem.</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 57 min od podania 18F-FDG. Glikemia: 117 mg%.</t>
+        </is>
+      </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>: Wzmożony metabolizm FDG w obrębie pierścienia Waldeyera SUV max do 5,5. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Aplazja prawej zatoki czołowej oraz znaczna hypoplazja lewej. Niewielkie lewowypukłe skrzywienie przegrody nosowej.  Klatka piersiowa i śródpiersie: Pobudzony metabolicznie węzeł chłonny pachowy lewy wielkości  13x9 mm SUV max 2,5 Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Na skórze przedniej części KLP na wysokości wyrostka mieczykowatego mostka, nieco na lewo od linii środkowej ciała - zmiana  brodawkowata średnicy ok 5 mm. Drobne zmiany włókniste w szczycie płuca lewego. Drobne zmiany włókniste i guzkowo-włókniste w szczycie płuca prawego. Drobne, obwodowe zmiany rozedmowo-włókniste w segm. 6 i 10 płuca prawego. Niewielkie zmiany włókniste obustronnie nadprzeponowo.  Brzuch i miednica: Aktywny metabolicznie naciek przykręgosłupowo po stronie prawej na poziomie od Th9/Th10 do Th11, wielkości 27x37x35 mm SUV max 11,0- masa miękkotkankowa/pakiet węzłowy.  Aktywne metabolicznie węzły chłonne pojedyncze i spakietowane: - dość liczne krezkowe wielkości do 18x13 mm SUV max do 15,3; - okołoaortalny lewy na poziomie L1 wielkości 15x9 mm SUV max 4,9; - okołoaortalny prawy na poziomie L2 średnicy 21 mm SUV max 11,1; - przykręgosłupowy prawy na poziomie L3 średnicy 16 mm SUV max 10,4; - prawobocznie przy rozwidleniu aorty oraz przy naczyniach biodrowych wspólnych i wewnętrznych prawych łącznej wielkości do 41x19x69 mm SUV max do 24,1; - przy naczyniach biodrowych zewnętrznych prawych wielkości do 15 mm SUV max do 6,5; - przy naczyniach biodrowych zewnętrznych lewych wielkości do 12 mm SUV max do 6,6.  Wzmożony metabolizm FDG w topografii endometrium i jamy macicy oraz w topografii przydatków lewych- w pierwszej kolejności o charakterze czynnościowym (OM 22.08.2022). Rozlanie wzmożony metabolizm FDG w śledzionie [o wymiarach: 141x67x109mm], SUV max do 5,5. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Torbiel w segmencie 5 wątroby średnicy 15 mm. Mierne pogrubienie nadnercza lewego na pograniczu trzonu i obu odnóg. Szyjka macicy o nieregularnych poszerzonych obrysach - do oceny w badaniu MR z kontrastem dożylnym i do kontroli ginekologicznej. W topografii przydatków prawych torbiel wielkości 35x44 mm.  Układ kostny: Aktywny metabolicznie  obszar w trzonie kości biodrowej lewej wielkości 17x27 mm wg PET SUV max 14,5 w topografii widocznej w przeglądowym badaniu TK niejednorodnej, miernie sklerotycznej przebudowy struktury kostnej. Poza tym fizjologiczny metabolizm FDG w układzie kostnym. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Wielopoziomowo dyskopatie i ciasne dyskopatie w odcinku szyjnym, piersiowym i lędźwiowym kregosłupa. Wielopoziomowo w obrębie blaszek granicznych trzonów kręgowych liczne drobne i wydatne guzki Schmorla. Osteolityczny obszar w dolno-prawobocznej części trzonu mostka średnicy 11 mm.  Wartości referencyjne: MBPS SUVmax 2,1; Prawy płat wątroby SUVmax do 3,4.</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Aktywna choroba</t>
+          <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność aktywnej metabolicznie choroby chłoniakowej z zajęciem kości biodrowej lewej oraz licznych węzłów chłonnych w jamie brzusznej i miednicy. Poza tym, jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G2" t="n">
         <v>24.1</v>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Baseline</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Nie dotyczy</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Aktywna metabolicznie choroba przed rozpoczęciem leczenia. Badanie wyjściowe stanowiące punkt odniesienia.</t>
-        </is>
-      </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
         <is>
           <t>07.11.2022</t>
         </is>
       </c>
-      <c r="B3" t="n">
-        <v>2</v>
-      </c>
       <c r="C3" t="inlineStr">
         <is>
           <t>Chłoniak Hodgkina- rozpoznanie z ww chłonnych pod MOS po stronie lewej. Ocena po 2 cyklach chemioterapii.</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 58 min od podania 18F-FDG. Glikemia: 110 mg%.</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>: Wzmożony metabolizm FDG w obrębie pierścienia Waldeyera SUV max do 4,3. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Aplazja prawej zatoki czołowej oraz znaczna hypoplazja lewej. Niewielkie lewowypukłe skrzywienie przegrody nosowej. Wydatne, przyścienne zgrubienia błony śluzowej wypełniające prawie całą prawą zatokę klinową - do pilnej konsultacji laryngologicznej.  Klatka piersiowa i śródpiersie: Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Na skórze przedniej części KLP na wysokości wyrostka mieczykowatego mostka, nieco na lewo od linii środkowej ciała - zmiana  brodawkowata średnicy ok 5 mm. Drobne zmiany włókniste w szczycie płuca lewego. Drobne zmiany włókniste i guzkowo-włókniste w szczycie płuca prawego. Drobne, obwodowe zmiany rozedmowo-włókniste w segm. 6 i 10 płuca prawego. Niewielkie zmiany włókniste obustronnie nadprzeponowo. Węzeł chłonny pachowe lewe wielkości do 11mm  Brzuch i miednica: Aktywny metabolicznie naciek przykręgosłupowo po stronie prawej na poziomie od Th9/Th10 do Th11, wielkości 20x33x31 mm SUV max 4,0- masa miękkotkankowa/pakiet węzłowy.  Aktywne metabolicznie węzły chłonne pojedyncze i spakietowane: - przykręgosłupowy prawy na poziomie trzonu kręgu L3 średnicy, 13 mm SUV max 5,0; - prawobocznie przy rozwidleniu aorty oraz przy naczyniach biodrowych wspólnych i wewnętrznych prawych o łącznej wielkości do 15x13x50 mm SUV max do 8,1; Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Dość liczne, nieaktywne metabolicznie węzły chłonne krezkowe, wielkości do 13mm. Torbiel w segmencie 5 wątroby średnicy 15 mm. Mierne pogrubienie nadnercza lewego na pograniczu trzonu i obu odnóg. Szyjka macicy o nieregularnych poszerzonych obrysach - do oceny w badaniu MR z kontrastem dożylnym i do kontroli ginekologicznej.  Układ kostny: Aktywny metabolicznie obszar w trzonie kości biodrowej lewej wielkości 10x23 mm wg PET SUV max 4,7 w topografii widocznej w przeglądowym badaniu TK niejednorodnej, miernie sklerotycznej przebudowy struktury kostnej. Poza tym niejednorodny metabolizm FDG w układzie kostnym objętym badaniem. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Wielopoziomowo dyskopatie i ciasne dyskopatie w odcinku szyjnym, piersiowym i lędźwiowym kregosłupa. Wielopoziomowo w obrębie blaszek granicznych trzonów kręgowych liczne drobne i wydatne guzki Schmorla. Osteolityczny obszar w dolno-prawobocznej części trzonu mostka średnicy 11 mm.  Wartości referencyjne: MBPS SUVmax 2,1; Prawy płat wątroby SUVmax do 3,1.</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność nadal aktywnej metabolicznie choroby chłoniakowej, z zajęciem kości biodrowej lewej oraz węzłów chłonnych w jamie brzusznej i miednicy. W porównaniu do badania poprzedniego PET z 06.09.2022 częściowa regresja ilości i wielkości opisywanych zmian. Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G3" t="n">
         <v>8.1</v>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>PR</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>4 - wychwyt umiarkowanie większy od wątroby</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Częściowa odpowiedź metaboliczna na leczenie. Klasyfikacja Lugano: Partial Response (PR) - częściowa odpowiedź na leczenie. Deauville: 4 - wychwyt umiarkowanie większy od wątroby.</t>
-        </is>
-      </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
         <is>
           <t>27.04.2023</t>
         </is>
       </c>
-      <c r="B4" t="n">
-        <v>3</v>
-      </c>
       <c r="C4" t="inlineStr">
         <is>
           <t>Chłoniak Hodgkina- rozpoznanie z ww chłonnych pod MOS po stronie lewej. Ocena po 2  miesiącach od zakończenia chemioterapii.</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 57 min od podania 18F-FDG. Glikemia: 103 mg%.</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>: Symetryczny metabolizm FDG w obrębie pierścienia Waldeyera SUV max do 4,6. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Aplazja prawej zatoki czołowej oraz znaczna hypoplazja lewej. Niewielkie lewowypukłe skrzywienie przegrody nosowej.  Klatka piersiowa i śródpiersie: Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Pogrubienie tkanek miękkich przykręgosłupowo po stronie prawej na poziomie od Th9/Th10 do Th11, do  8mm. Na skórze przedniej części KLP na wysokości wyrostka mieczykowatego mostka, nieco na lewo od linii środkowej ciała - zmiana  brodawkowata średnicy ok 5 mm. Drobne zmiany włókniste w szczytach płuc, drobne, obwodowe zmiany rozedmowo-włókniste płatach dolnych obu płuc obwodowo. Węzły chłonne pachowe średnicy do 11mm.  Brzuch i miednica: Aktywny metabolicznie naciek przykręgosłupowo, prawobocznie przy rozwidleniu aorty oraz przy naczyniach biodrowych wspólnych i wewnętrznych prawych o łącznej wielkości do 10x10x22mm SUV max do 4,4. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Dość liczne, nieaktywne metabolicznie węzły chłonne krezkowe, wielkości do 13mm. Torbiel w segmencie 5 wątroby średnicy 15 mm. Mierne pogrubienie nadnercza lewego na pograniczu trzonu i obu odnóg. Szyjka macicy o nieregularnych poszerzonych obrysach - do oceny w badaniu MR z kontrastem dożylnym i do kontroli ginekologicznej.  Układ kostny: Miernie aktywny metabolicznie obszar w trzonie kości biodrowej lewej wielkości 10x15mm wg PET SUV max 3,4 w topografii widocznej w przeglądowym badaniu TK niejednorodnej, miernie sklerotycznej przebudowy struktury kostnej. Poza tym niejednorodny metabolizm FDG w układzie kostnym objętym badaniem. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Wielopoziomowo dyskopatie i ciasne dyskopatie w odcinku szyjnym, piersiowym i lędźwiowym kregosłupa. Wielopoziomowo w obrębie blaszek granicznych trzonów kręgowych liczne drobne i wydatne guzki Schmorla. Osteolityczny obszar w dolno-prawobocznej części trzonu mostka średnicy 11 mm. Drobne zwapnienia w lewej kości biodrowej   Inne: Aktywność metaboliczna w brunatnej tkance tłuszczowej szyi i klatki piersiowej z widocznymi w jej obrębie pojedynczymi drobnymi węzłami chłonnymi, SUV max do 4,9 oraz mięśniach karku, SUV max do 8,9 - w pierwszej kolejności czynnościowa [lm fuz 108].   Wartości referencyjne: MBPS SUVmax 1,8; Prawy płat wątroby SUVmax do 3,1.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Aktywna choroba</t>
+          <t>Badaniem PET/CT z 18F-FDG uwidoczniono nadal obecność aktywnej metabolicznie choroby chłoniakowej, z zajęciem kości biodrowej lewej oraz węzłów chłonnych w jamie brzusznej. W porównaniu do badania poprzedniego PET z 07.11.2022 dalsza częściowa regresja ilości i wielkości opisywanych zmian. Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G4" t="n">
         <v>8.9</v>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>PR</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>4 - wychwyt umiarkowanie większy od wątroby</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Częściowa odpowiedź metaboliczna na leczenie. Klasyfikacja Lugano: Partial Response (PR) - częściowa odpowiedź na leczenie. Deauville: 4 - wychwyt umiarkowanie większy od wątroby.</t>
-        </is>
-      </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
         <is>
           <t>29.08.2023</t>
         </is>
       </c>
-      <c r="B5" t="n">
-        <v>4</v>
-      </c>
       <c r="C5" t="inlineStr">
         <is>
           <t>Chłoniak Hodgkina- rozpoznanie z ww chłonnych pod mMOS po stronie lewej. Badanie kontrolne w celu wykluczenia pierwotnej oporności choroby.</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 58 min od podania 18F-FDG. Glikemia: 105 mg%.</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>: Symetrycznie wzmożony metabolizm FDG w obrębie struktur pierścienia Waldeyera, SUV max do 7,7. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Aplazja prawej zatoki czołowej oraz znaczna hypoplazja lewej. Niewielkie lewowypukłe skrzywienie przegrody nosowej.  Klatka piersiowa i śródpiersie: W śródpiersiu przednim, zamostkowo, na poziomie dolnej krawędzi rękojeści mostka widoczna jest miękkotkankowa struktura obrębie tkanki tłuszczowej - SUV max 4,1 - jak poprzednio - powiększona grasica? Mniej prawdopodobne masy/węzły chłonne w przebiegu choroby zasadniczej-do oceny w badaniu TK KLP z kontrastem dożylnym. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Na skórze przedniej części KLP na wysokości wyrostka mieczykowatego mostka, nieco na lewo od linii środkowej ciała - zmiana  brodawkowata średnicy ok 5 mm. Drobne zmiany włókniste w szczycie płuca lewego. Drobne zmiany włókniste i guzkowo-włókniste w szczycie płuca prawego. Drobne, obwodowe zmiany rozedmowo-włókniste w segm. 6 i 10 płuca prawego. Niewielkie zmiany włókniste obustronnie nadprzeponowo. Węzły chłonne pachowe wielkości do 9x6mm.  Brzuch i miednica: Aktywne metabolicznie dość liczne węzły chłonne przykręgosłupowo po stronie prawej, od poziomu L2 do S1, wielkości do 23x15x32 mm, SUV max do  15,2.  Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Niewielkie pogrubienie tkanek miękkich przykręgosłupowo po stronie prawej, na poziomie Th9-Th11 - do 9mm - masa resztkowa nacieku. Dość liczne, nieaktywne metabolicznie węzły chłonne krezkowe, wielkości do 13mm. Torbiel w segmencie 5 wątroby wielkości 18x15 mm. Mierne pogrubienie nadnercza lewego na pograniczu trzonu i obu odnóg. Szyjka macicy o nieregularnych poszerzonych obrysach - do oceny w badaniu MR miednicy z kontrastem dożylnym i do kontroli ginekologicznej.  Układ kostny: Miernie aktywny metabolicznie obszar w trzonie kości biodrowej lewej, SUV max 2,9, w topografii widocznej w przeglądowym badaniu TK niejednorodnej, miernie sklerotycznej przebudowy struktury kostnej. Poza tym niejednorodny metabolizm FDG w układzie kostnym objętym badaniem. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Wielopoziomowo dyskopatie i ciasne dyskopatie w odcinku szyjnym, piersiowym i lędźwiowym kregosłupa. Wielopoziomowo w obrębie blaszek granicznych trzonów kręgowych liczne drobne i wydatne guzki Schmorla. Osteolityczny obszar w dolno-prawobocznej części trzonu mostka średnicy 11 mm. Drobne zwapnienia w lewej kości biodrowej.   Inne: Pobudzenie metaboliczne w lewym stawie biodrowym,  SUV max do 5,1- zmiany zwyrodnieniowo-przeciążeniowo-odczynowe.   Wartości referencyjne: MBPS SUVmax  2,5; Prawy płat wątroby SUVmax do 3,8.</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność nadal aktywnej metabolicznie choroby chłoniakowej, z zajęciem kości biodrowej lewej oraz węzłów chłonnych w jamie brzusznej. W porównaniu do badania poprzedniego PET z 27.04.2023r - progresja ilości i wielkości węzłów chłonnych. Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G5" t="n">
         <v>15.2</v>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>PD</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>5 - znacznie zwiększony wychwyt lub nowe zmiany</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Progresja choroby. Klasyfikacja Lugano: Progressive Disease (PD) - progresja choroby. Deauville: 5 - znacznie zwiększony wychwyt lub nowe zmiany.</t>
-        </is>
       </c>
     </row>
   </sheetData>

--- a/pacjenci/SYLWIA GMER.xlsx
+++ b/pacjenci/SYLWIA GMER.xlsx
@@ -413,13 +413,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Nr badania</t>
+          <t>Nr PET</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -439,17 +439,42 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Opis badania</t>
+          <t>Glikemia</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>Czas po FDG</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Głowa i szyja</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Klatka piersiowa</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Brzuch i miednica</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Układ kostny</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
           <t>Wnioski</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>SUVmax</t>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>SUVmax_global</t>
         </is>
       </c>
     </row>
@@ -469,20 +494,45 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 57 min od podania 18F-FDG. Glikemia: 117 mg%.</t>
+          <t>od szczytu głowy do 1/3 ud.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>: Wzmożony metabolizm FDG w obrębie pierścienia Waldeyera SUV max do 5,5. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Aplazja prawej zatoki czołowej oraz znaczna hypoplazja lewej. Niewielkie lewowypukłe skrzywienie przegrody nosowej.  Klatka piersiowa i śródpiersie: Pobudzony metabolicznie węzeł chłonny pachowy lewy wielkości  13x9 mm SUV max 2,5 Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Na skórze przedniej części KLP na wysokości wyrostka mieczykowatego mostka, nieco na lewo od linii środkowej ciała - zmiana  brodawkowata średnicy ok 5 mm. Drobne zmiany włókniste w szczycie płuca lewego. Drobne zmiany włókniste i guzkowo-włókniste w szczycie płuca prawego. Drobne, obwodowe zmiany rozedmowo-włókniste w segm. 6 i 10 płuca prawego. Niewielkie zmiany włókniste obustronnie nadprzeponowo.  Brzuch i miednica: Aktywny metabolicznie naciek przykręgosłupowo po stronie prawej na poziomie od Th9/Th10 do Th11, wielkości 27x37x35 mm SUV max 11,0- masa miękkotkankowa/pakiet węzłowy.  Aktywne metabolicznie węzły chłonne pojedyncze i spakietowane: - dość liczne krezkowe wielkości do 18x13 mm SUV max do 15,3; - okołoaortalny lewy na poziomie L1 wielkości 15x9 mm SUV max 4,9; - okołoaortalny prawy na poziomie L2 średnicy 21 mm SUV max 11,1; - przykręgosłupowy prawy na poziomie L3 średnicy 16 mm SUV max 10,4; - prawobocznie przy rozwidleniu aorty oraz przy naczyniach biodrowych wspólnych i wewnętrznych prawych łącznej wielkości do 41x19x69 mm SUV max do 24,1; - przy naczyniach biodrowych zewnętrznych prawych wielkości do 15 mm SUV max do 6,5; - przy naczyniach biodrowych zewnętrznych lewych wielkości do 12 mm SUV max do 6,6.  Wzmożony metabolizm FDG w topografii endometrium i jamy macicy oraz w topografii przydatków lewych- w pierwszej kolejności o charakterze czynnościowym (OM 22.08.2022). Rozlanie wzmożony metabolizm FDG w śledzionie [o wymiarach: 141x67x109mm], SUV max do 5,5. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Torbiel w segmencie 5 wątroby średnicy 15 mm. Mierne pogrubienie nadnercza lewego na pograniczu trzonu i obu odnóg. Szyjka macicy o nieregularnych poszerzonych obrysach - do oceny w badaniu MR z kontrastem dożylnym i do kontroli ginekologicznej. W topografii przydatków prawych torbiel wielkości 35x44 mm.  Układ kostny: Aktywny metabolicznie  obszar w trzonie kości biodrowej lewej wielkości 17x27 mm wg PET SUV max 14,5 w topografii widocznej w przeglądowym badaniu TK niejednorodnej, miernie sklerotycznej przebudowy struktury kostnej. Poza tym fizjologiczny metabolizm FDG w układzie kostnym. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Wielopoziomowo dyskopatie i ciasne dyskopatie w odcinku szyjnym, piersiowym i lędźwiowym kregosłupa. Wielopoziomowo w obrębie blaszek granicznych trzonów kręgowych liczne drobne i wydatne guzki Schmorla. Osteolityczny obszar w dolno-prawobocznej części trzonu mostka średnicy 11 mm.  Wartości referencyjne: MBPS SUVmax 2,1; Prawy płat wątroby SUVmax do 3,4.</t>
+          <t>117</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Wzmożony metabolizm FDG w obrębie pierścienia Waldeyera SUV max do 5,5. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Aplazja prawej zatoki czołowej oraz znaczna hypoplazja lewej. Niewielkie lewowypukłe skrzywienie przegrody nosowej.</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Pobudzony metabolicznie węzeł chłonny pachowy lewy wielkości  13x9 mm SUV max 2,5 Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Na skórze przedniej części KLP na wysokości wyrostka mieczykowatego mostka, nieco na lewo od linii środkowej ciała - zmiana  brodawkowata średnicy ok 5 mm. Drobne zmiany włókniste w szczycie płuca lewego. Drobne zmiany włókniste i guzkowo-włókniste w szczycie płuca prawego. Drobne, obwodowe zmiany rozedmowo-włókniste w segm. 6 i 10 płuca prawego. Niewielkie zmiany włókniste obustronnie nadprzeponowo.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Aktywny metabolicznie naciek przykręgosłupowo po stronie prawej na poziomie od Th9/Th10 do Th11, wielkości 27x37x35 mm SUV max 11,0- masa miękkotkankowa/pakiet węzłowy.  Aktywne metabolicznie węzły chłonne pojedyncze i spakietowane: - dość liczne krezkowe wielkości do 18x13 mm SUV max do 15,3; - okołoaortalny lewy na poziomie L1 wielkości 15x9 mm SUV max 4,9; - okołoaortalny prawy na poziomie L2 średnicy 21 mm SUV max 11,1; - przykręgosłupowy prawy na poziomie L3 średnicy 16 mm SUV max 10,4; - prawobocznie przy rozwidleniu aorty oraz przy naczyniach biodrowych wspólnych i wewnętrznych prawych łącznej wielkości do 41x19x69 mm SUV max do 24,1; - przy naczyniach biodrowych zewnętrznych prawych wielkości do 15 mm SUV max do 6,5; - przy naczyniach biodrowych zewnętrznych lewych wielkości do 12 mm SUV max do 6,6.  Wzmożony metabolizm FDG w topografii endometrium i jamy macicy oraz w topografii przydatków lewych- w pierwszej kolejności o charakterze czynnościowym (OM 22.08.2022). Rozlanie wzmożony metabolizm FDG w śledzionie [o wymiarach: 141x67x109mm], SUV max do 5,5. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Torbiel w segmencie 5 wątroby średnicy 15 mm. Mierne pogrubienie nadnercza lewego na pograniczu trzonu i obu odnóg. Szyjka macicy o nieregularnych poszerzonych obrysach - do oceny w badaniu MR z kontrastem dożylnym i do kontroli ginekologicznej. W topografii przydatków prawych torbiel wielkości 35x44 mm.</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Aktywny metabolicznie  obszar w trzonie kości biodrowej lewej wielkości 17x27 mm wg PET SUV max 14,5 w topografii widocznej w przeglądowym badaniu TK niejednorodnej, miernie sklerotycznej przebudowy struktury kostnej. Poza tym fizjologiczny metabolizm FDG w układzie kostnym. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Wielopoziomowo dyskopatie i ciasne dyskopatie w odcinku szyjnym, piersiowym i lędźwiowym kregosłupa. Wielopoziomowo w obrębie blaszek granicznych trzonów kręgowych liczne drobne i wydatne guzki Schmorla. Osteolityczny obszar w dolno-prawobocznej części trzonu mostka średnicy 11 mm.</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność aktywnej metabolicznie choroby chłoniakowej z zajęciem kości biodrowej lewej oraz licznych węzłów chłonnych w jamie brzusznej i miednicy. Poza tym, jak w opisie powyżej.</t>
         </is>
       </c>
-      <c r="G2" t="n">
+      <c r="L2" t="n">
         <v>24.1</v>
       </c>
     </row>
@@ -502,20 +552,45 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 58 min od podania 18F-FDG. Glikemia: 110 mg%.</t>
+          <t>od szczytu głowy do 1/3 ud.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>: Wzmożony metabolizm FDG w obrębie pierścienia Waldeyera SUV max do 4,3. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Aplazja prawej zatoki czołowej oraz znaczna hypoplazja lewej. Niewielkie lewowypukłe skrzywienie przegrody nosowej. Wydatne, przyścienne zgrubienia błony śluzowej wypełniające prawie całą prawą zatokę klinową - do pilnej konsultacji laryngologicznej.  Klatka piersiowa i śródpiersie: Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Na skórze przedniej części KLP na wysokości wyrostka mieczykowatego mostka, nieco na lewo od linii środkowej ciała - zmiana  brodawkowata średnicy ok 5 mm. Drobne zmiany włókniste w szczycie płuca lewego. Drobne zmiany włókniste i guzkowo-włókniste w szczycie płuca prawego. Drobne, obwodowe zmiany rozedmowo-włókniste w segm. 6 i 10 płuca prawego. Niewielkie zmiany włókniste obustronnie nadprzeponowo. Węzeł chłonny pachowe lewe wielkości do 11mm  Brzuch i miednica: Aktywny metabolicznie naciek przykręgosłupowo po stronie prawej na poziomie od Th9/Th10 do Th11, wielkości 20x33x31 mm SUV max 4,0- masa miękkotkankowa/pakiet węzłowy.  Aktywne metabolicznie węzły chłonne pojedyncze i spakietowane: - przykręgosłupowy prawy na poziomie trzonu kręgu L3 średnicy, 13 mm SUV max 5,0; - prawobocznie przy rozwidleniu aorty oraz przy naczyniach biodrowych wspólnych i wewnętrznych prawych o łącznej wielkości do 15x13x50 mm SUV max do 8,1; Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Dość liczne, nieaktywne metabolicznie węzły chłonne krezkowe, wielkości do 13mm. Torbiel w segmencie 5 wątroby średnicy 15 mm. Mierne pogrubienie nadnercza lewego na pograniczu trzonu i obu odnóg. Szyjka macicy o nieregularnych poszerzonych obrysach - do oceny w badaniu MR z kontrastem dożylnym i do kontroli ginekologicznej.  Układ kostny: Aktywny metabolicznie obszar w trzonie kości biodrowej lewej wielkości 10x23 mm wg PET SUV max 4,7 w topografii widocznej w przeglądowym badaniu TK niejednorodnej, miernie sklerotycznej przebudowy struktury kostnej. Poza tym niejednorodny metabolizm FDG w układzie kostnym objętym badaniem. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Wielopoziomowo dyskopatie i ciasne dyskopatie w odcinku szyjnym, piersiowym i lędźwiowym kregosłupa. Wielopoziomowo w obrębie blaszek granicznych trzonów kręgowych liczne drobne i wydatne guzki Schmorla. Osteolityczny obszar w dolno-prawobocznej części trzonu mostka średnicy 11 mm.  Wartości referencyjne: MBPS SUVmax 2,1; Prawy płat wątroby SUVmax do 3,1.</t>
+          <t>110</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Wzmożony metabolizm FDG w obrębie pierścienia Waldeyera SUV max do 4,3. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Aplazja prawej zatoki czołowej oraz znaczna hypoplazja lewej. Niewielkie lewowypukłe skrzywienie przegrody nosowej. Wydatne, przyścienne zgrubienia błony śluzowej wypełniające prawie całą prawą zatokę klinową - do pilnej konsultacji laryngologicznej.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Na skórze przedniej części KLP na wysokości wyrostka mieczykowatego mostka, nieco na lewo od linii środkowej ciała - zmiana  brodawkowata średnicy ok 5 mm. Drobne zmiany włókniste w szczycie płuca lewego. Drobne zmiany włókniste i guzkowo-włókniste w szczycie płuca prawego. Drobne, obwodowe zmiany rozedmowo-włókniste w segm. 6 i 10 płuca prawego. Niewielkie zmiany włókniste obustronnie nadprzeponowo. Węzeł chłonny pachowe lewe wielkości do 11mm</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Aktywny metabolicznie naciek przykręgosłupowo po stronie prawej na poziomie od Th9/Th10 do Th11, wielkości 20x33x31 mm SUV max 4,0- masa miękkotkankowa/pakiet węzłowy.  Aktywne metabolicznie węzły chłonne pojedyncze i spakietowane: - przykręgosłupowy prawy na poziomie trzonu kręgu L3 średnicy, 13 mm SUV max 5,0; - prawobocznie przy rozwidleniu aorty oraz przy naczyniach biodrowych wspólnych i wewnętrznych prawych o łącznej wielkości do 15x13x50 mm SUV max do 8,1; Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Dość liczne, nieaktywne metabolicznie węzły chłonne krezkowe, wielkości do 13mm. Torbiel w segmencie 5 wątroby średnicy 15 mm. Mierne pogrubienie nadnercza lewego na pograniczu trzonu i obu odnóg. Szyjka macicy o nieregularnych poszerzonych obrysach - do oceny w badaniu MR z kontrastem dożylnym i do kontroli ginekologicznej.</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Aktywny metabolicznie obszar w trzonie kości biodrowej lewej wielkości 10x23 mm wg PET SUV max 4,7 w topografii widocznej w przeglądowym badaniu TK niejednorodnej, miernie sklerotycznej przebudowy struktury kostnej. Poza tym niejednorodny metabolizm FDG w układzie kostnym objętym badaniem. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Wielopoziomowo dyskopatie i ciasne dyskopatie w odcinku szyjnym, piersiowym i lędźwiowym kregosłupa. Wielopoziomowo w obrębie blaszek granicznych trzonów kręgowych liczne drobne i wydatne guzki Schmorla. Osteolityczny obszar w dolno-prawobocznej części trzonu mostka średnicy 11 mm.</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność nadal aktywnej metabolicznie choroby chłoniakowej, z zajęciem kości biodrowej lewej oraz węzłów chłonnych w jamie brzusznej i miednicy. W porównaniu do badania poprzedniego PET z 06.09.2022 częściowa regresja ilości i wielkości opisywanych zmian. Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
-      <c r="G3" t="n">
+      <c r="L3" t="n">
         <v>8.1</v>
       </c>
     </row>
@@ -535,20 +610,45 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 57 min od podania 18F-FDG. Glikemia: 103 mg%.</t>
+          <t>od szczytu głowy do 1/3 ud.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>: Symetryczny metabolizm FDG w obrębie pierścienia Waldeyera SUV max do 4,6. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Aplazja prawej zatoki czołowej oraz znaczna hypoplazja lewej. Niewielkie lewowypukłe skrzywienie przegrody nosowej.  Klatka piersiowa i śródpiersie: Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Pogrubienie tkanek miękkich przykręgosłupowo po stronie prawej na poziomie od Th9/Th10 do Th11, do  8mm. Na skórze przedniej części KLP na wysokości wyrostka mieczykowatego mostka, nieco na lewo od linii środkowej ciała - zmiana  brodawkowata średnicy ok 5 mm. Drobne zmiany włókniste w szczytach płuc, drobne, obwodowe zmiany rozedmowo-włókniste płatach dolnych obu płuc obwodowo. Węzły chłonne pachowe średnicy do 11mm.  Brzuch i miednica: Aktywny metabolicznie naciek przykręgosłupowo, prawobocznie przy rozwidleniu aorty oraz przy naczyniach biodrowych wspólnych i wewnętrznych prawych o łącznej wielkości do 10x10x22mm SUV max do 4,4. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Dość liczne, nieaktywne metabolicznie węzły chłonne krezkowe, wielkości do 13mm. Torbiel w segmencie 5 wątroby średnicy 15 mm. Mierne pogrubienie nadnercza lewego na pograniczu trzonu i obu odnóg. Szyjka macicy o nieregularnych poszerzonych obrysach - do oceny w badaniu MR z kontrastem dożylnym i do kontroli ginekologicznej.  Układ kostny: Miernie aktywny metabolicznie obszar w trzonie kości biodrowej lewej wielkości 10x15mm wg PET SUV max 3,4 w topografii widocznej w przeglądowym badaniu TK niejednorodnej, miernie sklerotycznej przebudowy struktury kostnej. Poza tym niejednorodny metabolizm FDG w układzie kostnym objętym badaniem. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Wielopoziomowo dyskopatie i ciasne dyskopatie w odcinku szyjnym, piersiowym i lędźwiowym kregosłupa. Wielopoziomowo w obrębie blaszek granicznych trzonów kręgowych liczne drobne i wydatne guzki Schmorla. Osteolityczny obszar w dolno-prawobocznej części trzonu mostka średnicy 11 mm. Drobne zwapnienia w lewej kości biodrowej   Inne: Aktywność metaboliczna w brunatnej tkance tłuszczowej szyi i klatki piersiowej z widocznymi w jej obrębie pojedynczymi drobnymi węzłami chłonnymi, SUV max do 4,9 oraz mięśniach karku, SUV max do 8,9 - w pierwszej kolejności czynnościowa [lm fuz 108].   Wartości referencyjne: MBPS SUVmax 1,8; Prawy płat wątroby SUVmax do 3,1.</t>
+          <t>103</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Symetryczny metabolizm FDG w obrębie pierścienia Waldeyera SUV max do 4,6. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Aplazja prawej zatoki czołowej oraz znaczna hypoplazja lewej. Niewielkie lewowypukłe skrzywienie przegrody nosowej.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Pogrubienie tkanek miękkich przykręgosłupowo po stronie prawej na poziomie od Th9/Th10 do Th11, do  8mm. Na skórze przedniej części KLP na wysokości wyrostka mieczykowatego mostka, nieco na lewo od linii środkowej ciała - zmiana  brodawkowata średnicy ok 5 mm. Drobne zmiany włókniste w szczytach płuc, drobne, obwodowe zmiany rozedmowo-włókniste płatach dolnych obu płuc obwodowo. Węzły chłonne pachowe średnicy do 11mm.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Aktywny metabolicznie naciek przykręgosłupowo, prawobocznie przy rozwidleniu aorty oraz przy naczyniach biodrowych wspólnych i wewnętrznych prawych o łącznej wielkości do 10x10x22mm SUV max do 4,4. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Dość liczne, nieaktywne metabolicznie węzły chłonne krezkowe, wielkości do 13mm. Torbiel w segmencie 5 wątroby średnicy 15 mm. Mierne pogrubienie nadnercza lewego na pograniczu trzonu i obu odnóg. Szyjka macicy o nieregularnych poszerzonych obrysach - do oceny w badaniu MR z kontrastem dożylnym i do kontroli ginekologicznej.</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Miernie aktywny metabolicznie obszar w trzonie kości biodrowej lewej wielkości 10x15mm wg PET SUV max 3,4 w topografii widocznej w przeglądowym badaniu TK niejednorodnej, miernie sklerotycznej przebudowy struktury kostnej. Poza tym niejednorodny metabolizm FDG w układzie kostnym objętym badaniem. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Wielopoziomowo dyskopatie i ciasne dyskopatie w odcinku szyjnym, piersiowym i lędźwiowym kregosłupa. Wielopoziomowo w obrębie blaszek granicznych trzonów kręgowych liczne drobne i wydatne guzki Schmorla. Osteolityczny obszar w dolno-prawobocznej części trzonu mostka średnicy 11 mm. Drobne zwapnienia w lewej kości biodrowej   Inne: Aktywność metaboliczna w brunatnej tkance tłuszczowej szyi i klatki piersiowej z widocznymi w jej obrębie pojedynczymi drobnymi węzłami chłonnymi, SUV max do 4,9 oraz mięśniach karku, SUV max do 8,9 - w pierwszej kolejności czynnościowa [lm fuz 108].</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG uwidoczniono nadal obecność aktywnej metabolicznie choroby chłoniakowej, z zajęciem kości biodrowej lewej oraz węzłów chłonnych w jamie brzusznej. W porównaniu do badania poprzedniego PET z 07.11.2022 dalsza częściowa regresja ilości i wielkości opisywanych zmian. Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
-      <c r="G4" t="n">
+      <c r="L4" t="n">
         <v>8.9</v>
       </c>
     </row>
@@ -568,20 +668,45 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 58 min od podania 18F-FDG. Glikemia: 105 mg%.</t>
+          <t>od szczytu głowy do 1/3 ud.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>: Symetrycznie wzmożony metabolizm FDG w obrębie struktur pierścienia Waldeyera, SUV max do 7,7. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Aplazja prawej zatoki czołowej oraz znaczna hypoplazja lewej. Niewielkie lewowypukłe skrzywienie przegrody nosowej.  Klatka piersiowa i śródpiersie: W śródpiersiu przednim, zamostkowo, na poziomie dolnej krawędzi rękojeści mostka widoczna jest miękkotkankowa struktura obrębie tkanki tłuszczowej - SUV max 4,1 - jak poprzednio - powiększona grasica? Mniej prawdopodobne masy/węzły chłonne w przebiegu choroby zasadniczej-do oceny w badaniu TK KLP z kontrastem dożylnym. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Na skórze przedniej części KLP na wysokości wyrostka mieczykowatego mostka, nieco na lewo od linii środkowej ciała - zmiana  brodawkowata średnicy ok 5 mm. Drobne zmiany włókniste w szczycie płuca lewego. Drobne zmiany włókniste i guzkowo-włókniste w szczycie płuca prawego. Drobne, obwodowe zmiany rozedmowo-włókniste w segm. 6 i 10 płuca prawego. Niewielkie zmiany włókniste obustronnie nadprzeponowo. Węzły chłonne pachowe wielkości do 9x6mm.  Brzuch i miednica: Aktywne metabolicznie dość liczne węzły chłonne przykręgosłupowo po stronie prawej, od poziomu L2 do S1, wielkości do 23x15x32 mm, SUV max do  15,2.  Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Niewielkie pogrubienie tkanek miękkich przykręgosłupowo po stronie prawej, na poziomie Th9-Th11 - do 9mm - masa resztkowa nacieku. Dość liczne, nieaktywne metabolicznie węzły chłonne krezkowe, wielkości do 13mm. Torbiel w segmencie 5 wątroby wielkości 18x15 mm. Mierne pogrubienie nadnercza lewego na pograniczu trzonu i obu odnóg. Szyjka macicy o nieregularnych poszerzonych obrysach - do oceny w badaniu MR miednicy z kontrastem dożylnym i do kontroli ginekologicznej.  Układ kostny: Miernie aktywny metabolicznie obszar w trzonie kości biodrowej lewej, SUV max 2,9, w topografii widocznej w przeglądowym badaniu TK niejednorodnej, miernie sklerotycznej przebudowy struktury kostnej. Poza tym niejednorodny metabolizm FDG w układzie kostnym objętym badaniem. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Wielopoziomowo dyskopatie i ciasne dyskopatie w odcinku szyjnym, piersiowym i lędźwiowym kregosłupa. Wielopoziomowo w obrębie blaszek granicznych trzonów kręgowych liczne drobne i wydatne guzki Schmorla. Osteolityczny obszar w dolno-prawobocznej części trzonu mostka średnicy 11 mm. Drobne zwapnienia w lewej kości biodrowej.   Inne: Pobudzenie metaboliczne w lewym stawie biodrowym,  SUV max do 5,1- zmiany zwyrodnieniowo-przeciążeniowo-odczynowe.   Wartości referencyjne: MBPS SUVmax  2,5; Prawy płat wątroby SUVmax do 3,8.</t>
+          <t>105</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Symetrycznie wzmożony metabolizm FDG w obrębie struktur pierścienia Waldeyera, SUV max do 7,7. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Aplazja prawej zatoki czołowej oraz znaczna hypoplazja lewej. Niewielkie lewowypukłe skrzywienie przegrody nosowej.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>W śródpiersiu przednim, zamostkowo, na poziomie dolnej krawędzi rękojeści mostka widoczna jest miękkotkankowa struktura obrębie tkanki tłuszczowej - SUV max 4,1 - jak poprzednio - powiększona grasica? Mniej prawdopodobne masy/węzły chłonne w przebiegu choroby zasadniczej-do oceny w badaniu TK KLP z kontrastem dożylnym. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Na skórze przedniej części KLP na wysokości wyrostka mieczykowatego mostka, nieco na lewo od linii środkowej ciała - zmiana  brodawkowata średnicy ok 5 mm. Drobne zmiany włókniste w szczycie płuca lewego. Drobne zmiany włókniste i guzkowo-włókniste w szczycie płuca prawego. Drobne, obwodowe zmiany rozedmowo-włókniste w segm. 6 i 10 płuca prawego. Niewielkie zmiany włókniste obustronnie nadprzeponowo. Węzły chłonne pachowe wielkości do 9x6mm.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Aktywne metabolicznie dość liczne węzły chłonne przykręgosłupowo po stronie prawej, od poziomu L2 do S1, wielkości do 23x15x32 mm, SUV max do  15,2.  Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Niewielkie pogrubienie tkanek miękkich przykręgosłupowo po stronie prawej, na poziomie Th9-Th11 - do 9mm - masa resztkowa nacieku. Dość liczne, nieaktywne metabolicznie węzły chłonne krezkowe, wielkości do 13mm. Torbiel w segmencie 5 wątroby wielkości 18x15 mm. Mierne pogrubienie nadnercza lewego na pograniczu trzonu i obu odnóg. Szyjka macicy o nieregularnych poszerzonych obrysach - do oceny w badaniu MR miednicy z kontrastem dożylnym i do kontroli ginekologicznej.</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Miernie aktywny metabolicznie obszar w trzonie kości biodrowej lewej, SUV max 2,9, w topografii widocznej w przeglądowym badaniu TK niejednorodnej, miernie sklerotycznej przebudowy struktury kostnej. Poza tym niejednorodny metabolizm FDG w układzie kostnym objętym badaniem. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Wielopoziomowo dyskopatie i ciasne dyskopatie w odcinku szyjnym, piersiowym i lędźwiowym kregosłupa. Wielopoziomowo w obrębie blaszek granicznych trzonów kręgowych liczne drobne i wydatne guzki Schmorla. Osteolityczny obszar w dolno-prawobocznej części trzonu mostka średnicy 11 mm. Drobne zwapnienia w lewej kości biodrowej.   Inne: Pobudzenie metaboliczne w lewym stawie biodrowym,  SUV max do 5,1- zmiany zwyrodnieniowo-przeciążeniowo-odczynowe.</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność nadal aktywnej metabolicznie choroby chłoniakowej, z zajęciem kości biodrowej lewej oraz węzłów chłonnych w jamie brzusznej. W porównaniu do badania poprzedniego PET z 27.04.2023r - progresja ilości i wielkości węzłów chłonnych. Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
-      <c r="G5" t="n">
+      <c r="L5" t="n">
         <v>15.2</v>
       </c>
     </row>
